--- a/Assets/Config/Excel/怪物配置.xlsx
+++ b/Assets/Config/Excel/怪物配置.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Projects\Joker_MMO_Clone\Assets\Config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Projects\Joker_MMO\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A665D2CB-C378-45EA-9DBD-60E90D4FFF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C346F534-964B-4793-BE7D-7DFD55E33480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1788" yWindow="2652" windowWidth="22284" windowHeight="13476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -559,7 +559,7 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -588,7 +588,7 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -617,7 +617,7 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -646,7 +646,7 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -675,7 +675,7 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -704,7 +704,7 @@
         <v>13</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -733,7 +733,7 @@
         <v>15</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F8">
         <v>5</v>
